--- a/mahasiswa_2022.xlsx
+++ b/mahasiswa_2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junaidisurya/si_unh_website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E76E503-0FE4-414F-AFBB-13F26904A287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8C5A1C-F2B9-BF4F-A99B-B730195CA308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="1000" windowWidth="25040" windowHeight="13540" xr2:uid="{F33CED50-82CB-9244-AB4A-9750830964C0}"/>
   </bookViews>
